--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1939</v>
+        <v>2535</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1361</v>
+        <v>1768</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>520</v>
+        <v>685</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -802,12 +802,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>53815</t>
+          <t>05635</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -817,56 +817,56 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>237</v>
+        <v>135</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05635</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>92</v>
+        <v>4</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,104 +910,104 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>53815</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
+        <v>178</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>293</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="M13" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>114</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L13" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="M13" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1145,47 +1145,47 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1199,155 +1199,155 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,35 +1357,35 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="J21" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>139</v>
+      </c>
+      <c r="M21" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,50 +1396,50 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="F22" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="I22" s="12" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,158 +1450,158 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,101 +1612,101 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>18</v>
+        <v>291</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -1739,47 +1739,47 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,23 +1789,23 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>9</v>
@@ -1814,26 +1814,26 @@
         <v>13</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J31" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L31" s="12" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,101 +1955,101 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L32" s="12" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>COTIGNOLA</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2063,82 +2063,82 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>COTIGNOLA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>1</v>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K37" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2279,31 +2279,31 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2333,85 +2333,81 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H39" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="I39" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>15</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>RAVENNA</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="K40" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,28 +2437,28 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
@@ -2476,12 +2472,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2495,31 +2491,31 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J42" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K42" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,46 +2526,50 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+          <t>PORTO SAN GIORGIO</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2580,66 +2580,66 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>06148</t>
+          <t>05625</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CAGLI</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>06148</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>CAGLI</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>0</v>
@@ -2668,74 +2668,74 @@
         <v>2</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05625</t>
+          <t>53821</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2764,13 +2764,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>158</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.7278481012658228</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>137</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.0291970802919708</v>
+        <v>4</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>206</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.6456310679611651</v>
+        <v>133</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>89</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.1348314606741573</v>
+        <v>12</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.13</v>
+        <v>13</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>161</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.6459627329192547</v>
+        <v>104</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>152</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.0131578947368421</v>
+        <v>2</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>105</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3904761904761905</v>
+        <v>41</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>154</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.02597402597402598</v>
+        <v>4</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>185</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>5</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>139</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.04316546762589928</v>
+        <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>80</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.025</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>96</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.01041666666666667</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.2248062015503876</v>
+        <v>29</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>108</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.3888888888888889</v>
+        <v>42</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>98</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.01020408163265306</v>
+        <v>1</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>66</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.01515151515151515</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>55</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.01818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>39</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.1538461538461539</v>
+        <v>6</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>67</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.01492537313432836</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>37</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>68</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.02941176470588235</v>
+        <v>2</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>22</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.09090909090909091</v>
+        <v>2</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>15</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>10</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2515,7 +2515,7 @@
         <v>37</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.5945945945945946</v>
+        <v>22</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2535</v>
+        <v>2681</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1768</v>
+        <v>1862</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>685</v>
+        <v>725</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -802,17 +802,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05635</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -856,66 +856,66 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>53815</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>171</v>
+        <v>309</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>53815</t>
+          <t>05635</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,51 +925,51 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>JESI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>JESI</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1145,47 +1145,47 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1199,143 +1199,143 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F18" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="I18" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="G18" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>100</v>
-      </c>
       <c r="J18" s="12" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>154</v>
+        <v>194</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>22</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
@@ -1504,108 +1504,108 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1634,13 +1634,13 @@
         <v>64</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>96</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>38</v>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>30</v>
@@ -1757,10 +1757,10 @@
         <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>4</v>
@@ -1805,19 +1805,19 @@
         <v>1</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1850,13 +1850,13 @@
         <v>38</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>34</v>
@@ -1875,19 +1875,19 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
         <v>36</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,47 +1955,47 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" s="12" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K32" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="M32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L32" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2063,35 +2063,35 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
         <v>32</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>1</v>
@@ -2171,19 +2171,19 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>8</v>
@@ -2192,7 +2192,7 @@
         <v>5</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>1</v>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2225,82 +2225,82 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>2</v>
@@ -2314,54 +2314,54 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L39" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="M39" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2437,19 +2437,19 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>22</v>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>0</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>50</v>
@@ -2611,16 +2611,16 @@
         <v>21</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -2728,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -2764,13 +2764,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
@@ -2864,13 +2864,13 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2376,7 +2376,11 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -2804,7 +2808,11 @@
           <t>MONTECOSARO</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
@@ -2854,7 +2862,11 @@
           <t>CORRIDONIA</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2681</v>
+        <v>2877</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1862</v>
+        <v>1987</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>725</v>
+        <v>774</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -802,12 +802,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>53815</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -817,51 +817,51 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>193</v>
+        <v>327</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="L11" s="12" t="n">
+        <v>229</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="M11" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>53815</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,39 +871,39 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>309</v>
+        <v>203</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>221</v>
+        <v>149</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>142</v>
+        <v>4</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>36</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>36</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>84</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>14</v>
@@ -1072,50 +1072,50 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1199,89 +1199,89 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="G18" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="H18" s="12" t="n">
-        <v>95</v>
-      </c>
       <c r="I18" s="12" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G21" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>76</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>75</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>22</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>4</v>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>8</v>
@@ -1595,10 +1595,10 @@
         <v>21</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>29</v>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,66 +1828,66 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,14 +1897,14 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>5</v>
@@ -1913,35 +1913,35 @@
         <v>2</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,105 +2059,105 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>COTIGNOLA</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,50 +2260,50 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>COTIGNOLA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2333,89 +2333,89 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2441,28 +2441,28 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>22</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>9</v>
@@ -2516,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>0</v>
@@ -2567,17 +2567,17 @@
         <v>3</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>50</v>
@@ -2621,10 +2621,10 @@
         <v>1</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2877</v>
+        <v>3034</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1987</v>
+        <v>2101</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>774</v>
+        <v>807</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>78</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>4</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>40</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>14</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>14</v>
@@ -1072,104 +1072,104 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>50</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>41</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>42</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>2</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>5</v>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>77</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>22</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>4</v>
@@ -1450,108 +1450,108 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1688,13 +1688,13 @@
         <v>63</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>48</v>
@@ -1706,7 +1706,7 @@
         <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -1720,54 +1720,54 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K28" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L28" s="12" t="n">
-        <v>109</v>
-      </c>
       <c r="M28" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1793,25 +1793,25 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>64</v>
@@ -1828,54 +1828,54 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>17</v>
+        <v>112</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>5</v>
@@ -1919,10 +1919,10 @@
         <v>4</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>1</v>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
@@ -2138,10 +2138,10 @@
         <v>13</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2192,14 +2192,14 @@
         <v>11</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>2</v>
@@ -2237,7 +2237,7 @@
         <v>8</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>10</v>
@@ -2282,7 +2282,7 @@
         <v>32</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>1</v>
@@ -2333,16 +2333,16 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>29</v>
@@ -2351,10 +2351,10 @@
         <v>11</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>2</v>
@@ -2387,28 +2387,28 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="I40" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>2</v>
@@ -2444,13 +2444,13 @@
         <v>19</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>13</v>
@@ -2462,7 +2462,7 @@
         <v>6</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
@@ -2516,14 +2516,14 @@
         <v>0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2570,7 @@
         <v>5</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>50</v>
@@ -2621,10 +2621,10 @@
         <v>1</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>39</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3034</v>
+        <v>3238</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2101</v>
+        <v>2259</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>807</v>
+        <v>862</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>152</v>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>4</v>
@@ -929,47 +929,47 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>JESI</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,32 +979,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>88</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>14</v>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>JESI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,39 +1033,39 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>5</v>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F18" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I18" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="G18" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>118</v>
-      </c>
       <c r="J18" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>41</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>42</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>2</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>5</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>6</v>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,104 +1504,104 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>363</v>
+        <v>393</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>1</v>
@@ -1688,13 +1688,13 @@
         <v>63</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>48</v>
@@ -1706,7 +1706,7 @@
         <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -1739,22 +1739,22 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>3</v>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>33</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J31" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K31" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K31" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="L31" s="12" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,39 +2059,39 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
@@ -2135,29 +2135,29 @@
         <v>9</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,39 +2221,39 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
         <v>32</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>1</v>
@@ -2342,7 +2342,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>29</v>
@@ -2354,7 +2354,7 @@
         <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>2</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>43</v>
@@ -2396,22 +2396,22 @@
         <v>27</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,19 +2441,19 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
@@ -2462,7 +2462,7 @@
         <v>6</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
@@ -2516,14 +2516,14 @@
         <v>0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>50</v>
@@ -2615,16 +2615,16 @@
         <v>21</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -2754,11 +2754,7 @@
           <t>PESARO</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
@@ -2808,11 +2804,7 @@
           <t>MONTECOSARO</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
@@ -2862,11 +2854,7 @@
           <t>CORRIDONIA</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -918,11 +918,7 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -1728,11 +1724,7 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -2268,11 +2260,7 @@
           <t>COTIGNOLA</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
@@ -2592,11 +2580,7 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N49" headerRowCount="1">
-  <autoFilter ref="A10:N49"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O49" headerRowCount="1">
+  <autoFilter ref="A10:O49"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>VIA CONSOLARE SAN MARINO 7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>247</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>356</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA EMILIA, 1837</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -918,40 +944,45 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>VIA ROMEA NORD 102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>171</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -970,42 +1001,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA SALVO D'ACQUISTO 121</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>185</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1024,42 +1060,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA ANCONA 68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>185</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1078,42 +1119,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>S.S.423 LOC.TORRACCIA</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1132,42 +1178,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>GRANAROLO, 177</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1186,42 +1237,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>MANZONI LOC. VILLA PAPA</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1240,42 +1296,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>VIA CARDUCCI</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>192</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>186</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1294,42 +1355,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>VIA E. MATTEI, 28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>164</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1348,42 +1414,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1402,42 +1473,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>VIA ROMEA 1498</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>CELLINI LUCA</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1456,42 +1532,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>VIA CALCINARO 2460</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>CELLINI LUCA</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1510,42 +1591,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>VIA FLAMINIA 3</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1564,42 +1650,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>VIA ROMA</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1618,42 +1709,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>VIA EUGENIO BERTINI</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>CELLINI LUCA</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>393</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1672,42 +1768,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>VIA DELLA MONTAGNOLA N.24</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="M27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1724,40 +1825,45 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>TRIESTE 0290</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1776,42 +1882,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>VIA BERNINI</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1830,42 +1941,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>FRAZ. ASPIO SS 16</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="M30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1884,42 +2000,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1938,42 +2059,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1992,42 +2118,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>PROV.LE ARCEVIESE</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2046,42 +2177,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>S.PROV.ALLACCIANTE</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2100,42 +2236,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>VIA MARCO POLO 238</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2154,42 +2295,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2208,42 +2354,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2260,40 +2411,45 @@
           <t>COTIGNOLA</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>VIA MADONNA DI GENOVA, 23/A</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2312,42 +2468,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="L39" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="M39" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2366,42 +2527,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>MARECCHIESE LOC SPAD</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>CELLINI LUCA</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="M40" s="12" t="n">
+      <c r="N40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2420,42 +2586,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="I41" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="J41" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="M41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2474,42 +2645,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2528,20 +2704,22 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
       </c>
@@ -2549,21 +2727,24 @@
         <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="M43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2580,40 +2761,45 @@
           <t>RAVENNA</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>VIA RAVEGNANA,  329</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="K44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K44" s="12" t="n">
+      <c r="L44" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="M44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2632,20 +2818,22 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>VIA FLAMINIA</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G45" s="12" t="n">
         <v>0</v>
       </c>
@@ -2653,21 +2841,24 @@
         <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="K45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="M45" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2686,42 +2877,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>SS 16 ADRIATICA KM 237+192 S.N.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H46" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="M46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2738,27 +2934,29 @@
           <t>PESARO</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr"/>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>STRADA DELLE REGIONI KM 6 + 531</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="G47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J47" s="12" t="n">
         <v>0</v>
       </c>
@@ -2771,7 +2969,10 @@
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="N47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2788,27 +2989,29 @@
           <t>MONTECOSARO</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>SS 485 KM8+126 STAZ.DI MONTECOSARO</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J48" s="12" t="n">
         <v>0</v>
       </c>
@@ -2821,7 +3024,10 @@
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2838,27 +3044,29 @@
           <t>CORRIDONIA</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>PAUSOLA ZONA INDUSTRIALE</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J49" s="12" t="n">
         <v>0</v>
       </c>
@@ -2871,7 +3079,10 @@
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="N49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O49" headerRowCount="1">
-  <autoFilter ref="A10:O49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O50" headerRowCount="1">
+  <autoFilter ref="A10:O50"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3238</v>
+        <v>3387</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2259</v>
+        <v>2360</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>862</v>
+        <v>918</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -877,114 +877,114 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>05635</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 1837</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>VIA ROMEA NORD 102</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>4</v>
+        <v>143</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05635</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMEA NORD 102</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
+          <t>VIA EMILIA, 1837</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>197</v>
+        <v>158</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,31 +1074,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1109,55 +1109,55 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>S.S.423 LOC.TORRACCIA</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="I16" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>139</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>65</v>
-      </c>
       <c r="L16" s="12" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>203</v>
+        <v>253</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1168,55 +1168,55 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>S.S.423 LOC.TORRACCIA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>5</v>
+        <v>133</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1251,35 +1251,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>41</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1310,28 +1310,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>199</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L19" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="M19" s="12" t="n">
         <v>192</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>122</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>186</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>5</v>
@@ -1428,28 +1428,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I21" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L21" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J21" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>52</v>
-      </c>
       <c r="M21" s="12" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1487,16 +1487,16 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>44</v>
@@ -1505,10 +1505,10 @@
         <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>5</v>
@@ -1546,28 +1546,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>32</v>
@@ -1605,35 +1605,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>81</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1664,28 +1664,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>1</v>
@@ -1723,31 +1723,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1782,16 +1782,16 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>48</v>
@@ -1800,10 +1800,10 @@
         <v>15</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1837,22 +1837,22 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>3</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>7</v>
@@ -1908,16 +1908,16 @@
         <v>3</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
@@ -1931,17 +1931,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1955,52 +1955,52 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2014,35 +2014,35 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>5</v>
@@ -2091,10 +2091,10 @@
         <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>1</v>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>5</v>
@@ -2144,7 +2144,7 @@
         <v>2</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>6</v>
@@ -2153,21 +2153,21 @@
         <v>13</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>8</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2191,52 +2191,52 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2246,39 +2246,39 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2309,28 +2309,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>1</v>
@@ -2344,17 +2344,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2368,86 +2368,90 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K37" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L37" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>COTIGNOLA</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA MADONNA DI GENOVA, 23/A</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr"/>
+          <t>VIA MARCO POLO 238</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="N38" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2458,55 +2462,51 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>COTIGNOLA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA MADONNA DI GENOVA, 23/A</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="H39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="M39" s="12" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2541,31 +2541,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>34</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>14</v>
@@ -2621,7 +2621,7 @@
         <v>6</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
@@ -2635,76 +2635,72 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>05625</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA RAVEGNANA,  329</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" s="12" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2718,31 +2714,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2753,107 +2749,107 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05625</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA RAVEGNANA,  329</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>06148</t>
+          <t>05993</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CAGLI</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L45" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
@@ -2867,17 +2863,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>06148</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>CAGLI</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SS 16 ADRIATICA KM 237+192 S.N.</t>
+          <t>VIA FLAMINIA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2891,13 +2887,13 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>0</v>
@@ -2909,10 +2905,10 @@
         <v>1</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2926,7 +2922,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>06128</t>
+          <t>53821</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2936,81 +2932,85 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>STRADA DELLE REGIONI KM 6 + 531</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>SS 16 ADRIATICA KM 237+192 S.N.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>06812</t>
+          <t>06128</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MONTECOSARO</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>SS 485 KM8+126 STAZ.DI MONTECOSARO</t>
+          <t>STRADA DELLE REGIONI KM 6 + 531</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>0</v>
@@ -3029,60 +3029,115 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>51486</t>
+          <t>06812</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CORRIDONIA</t>
+          <t>MONTECOSARO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>PAUSOLA ZONA INDUSTRIALE</t>
+          <t>SS 485 KM8+126 STAZ.DI MONTECOSARO</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>STROLOGO FRANCESCO</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>51486</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDONIA</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>PAUSOLA ZONA INDUSTRIALE</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="F49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="12" t="n">
+      <c r="F50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="H49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="12" t="n">
+      <c r="H50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
+      <c r="J50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>40</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3387</v>
+        <v>3521</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2360</v>
+        <v>2457</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>918</v>
+        <v>967</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>48</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         <v>229</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>146</v>
@@ -991,17 +991,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>S.S.423 LOC.TORRACCIA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1011,39 +1011,39 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>120</v>
+        <v>218</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>15</v>
@@ -1109,55 +1109,55 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>253</v>
+        <v>125</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1168,55 +1168,55 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>S.S.423 LOC.TORRACCIA</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1251,35 +1251,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1310,28 +1310,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>5</v>
@@ -1428,35 +1428,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1487,31 +1487,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1546,31 +1546,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>40</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1605,35 +1605,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1664,28 +1664,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>1</v>
@@ -1723,28 +1723,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1782,19 +1782,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>15</v>
@@ -1803,7 +1803,7 @@
         <v>19</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
         <v>25</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>2</v>
@@ -1955,35 +1955,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>7</v>
@@ -2032,10 +2032,10 @@
         <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2073,19 +2073,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>4</v>
@@ -2094,7 +2094,7 @@
         <v>31</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>1</v>
@@ -2132,28 +2132,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>8</v>
@@ -2167,17 +2167,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2187,39 +2187,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K34" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L34" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="M34" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
@@ -2262,16 +2262,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2285,17 +2285,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2305,39 +2305,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K36" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>44</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2371,13 +2371,13 @@
         <v>36</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>32</v>
@@ -2389,10 +2389,10 @@
         <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>2</v>
@@ -2462,51 +2462,55 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>COTIGNOLA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA MADONNA DI GENOVA, 23/A</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>MARECCHIESE LOC SPAD</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H39" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>113</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="I39" s="12" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K39" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L39" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L39" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="M39" s="12" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2517,55 +2521,51 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>COTIGNOLA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>VIA MADONNA DI GENOVA, 23/A</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>28</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2576,114 +2576,114 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>05625</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA RAVEGNANA,  329</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05625</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA RAVEGNANA,  329</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G42" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I42" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H42" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="J42" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2714,31 +2714,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2773,28 +2773,28 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
@@ -2828,28 +2828,28 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>40</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3521</v>
+        <v>3675</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2457</v>
+        <v>2560</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>967</v>
+        <v>1018</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>90</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>75</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>48</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>114</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         <v>229</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>146</v>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H14" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="I14" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="J14" s="12" t="n">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>15</v>
@@ -1109,55 +1109,55 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>164</v>
+        <v>107</v>
       </c>
       <c r="K16" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="L16" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="M16" s="12" t="n">
-        <v>125</v>
+        <v>284</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1168,59 +1168,59 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>42</v>
+        <v>96</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>269</v>
+        <v>129</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1251,31 +1251,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1310,28 +1310,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>5</v>
@@ -1428,28 +1428,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1487,16 +1487,16 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>45</v>
@@ -1505,13 +1505,13 @@
         <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1546,35 +1546,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1605,35 +1605,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1664,28 +1664,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>1</v>
@@ -1723,28 +1723,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1782,28 +1782,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1817,72 +1817,76 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE 0290</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>VIA BERNINI</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1892,35 +1896,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1931,59 +1935,55 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>TRIESTE 0290</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="K30" s="12" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2073,16 +2073,16 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>20</v>
@@ -2091,10 +2091,10 @@
         <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>1</v>
@@ -2132,16 +2132,16 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>27</v>
@@ -2150,10 +2150,10 @@
         <v>6</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>8</v>
@@ -2167,55 +2167,55 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K34" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="N34" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2250,31 +2250,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2285,17 +2285,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2305,56 +2305,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K36" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L36" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L36" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="M36" s="12" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2368,52 +2368,52 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2423,35 +2423,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
         <v>36</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L38" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2462,55 +2462,55 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L39" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L39" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="M39" s="12" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2544,13 +2544,13 @@
         <v>32</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>28</v>
@@ -2596,19 +2596,19 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>50</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>1</v>
@@ -2617,7 +2617,7 @@
         <v>9</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
@@ -2658,13 +2658,13 @@
         <v>21</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>15</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
@@ -2735,14 +2735,14 @@
         <v>1</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2794,14 +2794,14 @@
         <v>5</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>40</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3675</v>
+        <v>3776</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2560</v>
+        <v>2640</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1018</v>
+        <v>1055</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>157</v>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>114</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>54</v>
-      </c>
       <c r="M12" s="12" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -932,118 +932,118 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 1837</t>
+          <t>S.S.423 LOC.TORRACCIA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>275</v>
+        <v>178</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>158</v>
+        <v>253</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>4</v>
+        <v>153</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>S.S.423 LOC.TORRACCIA</t>
+          <t>VIA EMILIA, 1837</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>175</v>
+        <v>283</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>241</v>
+        <v>158</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>48</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>15</v>
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>95</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1192,28 +1192,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>15</v>
@@ -1251,35 +1251,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>53</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1310,28 +1310,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1345,22 +1345,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA E. MATTEI, 28</t>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1369,57 +1369,57 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="H20" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="N20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>103</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>204</v>
-      </c>
-      <c r="N20" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE ADRIATICA 148</t>
+          <t>VIA E. MATTEI, 28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>9</v>
@@ -1546,28 +1546,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>44</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>34</v>
@@ -1581,118 +1581,118 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G24" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="J24" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="H24" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>93</v>
-      </c>
       <c r="K24" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1723,28 +1723,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1785,13 +1785,13 @@
         <v>75</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>57</v>
@@ -1803,7 +1803,7 @@
         <v>21</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>8</v>
@@ -1853,16 +1853,16 @@
         <v>6</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1903,7 +1903,7 @@
         <v>61</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>31</v>
@@ -2017,7 +2017,7 @@
         <v>54</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>8</v>
@@ -2035,7 +2035,7 @@
         <v>22</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>7</v>
@@ -2091,10 +2091,10 @@
         <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>1</v>
@@ -2108,125 +2108,125 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="N33" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2250,31 +2250,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H35" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="M35" s="12" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2285,17 +2285,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2305,56 +2305,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="J36" s="12" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2364,39 +2364,39 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>3</v>
@@ -2439,16 +2439,16 @@
         <v>10</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>4</v>
@@ -2486,28 +2486,28 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>2</v>
@@ -2544,7 +2544,7 @@
         <v>32</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
@@ -2658,13 +2658,13 @@
         <v>21</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>15</v>
@@ -2676,31 +2676,31 @@
         <v>6</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2714,149 +2714,149 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>05993</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05993</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr"/>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>40</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3776</v>
+        <v>3954</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2640</v>
+        <v>2759</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1055</v>
+        <v>1137</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>157</v>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>50</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>115</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>153</v>
@@ -956,35 +956,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1018,13 +1018,13 @@
         <v>229</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>146</v>
@@ -1074,31 +1074,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1133,28 +1133,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>8</v>
@@ -1192,28 +1192,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>15</v>
@@ -1227,17 +1227,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MANZONI LOC. VILLA PAPA</t>
+          <t>VIA CARDUCCI</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,153 +1251,153 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA CARDUCCI</t>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE ADRIATICA 148</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M20" s="12" t="n">
         <v>168</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>182</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>217</v>
-      </c>
       <c r="N20" s="12" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1428,31 +1428,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>39</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>9</v>
@@ -1522,17 +1522,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA CALCINARO 2460</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1542,94 +1542,94 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>VIA CALCINARO 2460</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1640,59 +1640,59 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1723,28 +1723,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>494</v>
+        <v>525</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1782,28 +1782,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1841,28 +1841,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1903,13 +1903,13 @@
         <v>61</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>31</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>54</v>
@@ -1921,7 +1921,7 @@
         <v>6</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1976,7 +1976,7 @@
         <v>3</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>12</v>
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>16</v>
@@ -2032,10 +2032,10 @@
         <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>7</v>
@@ -2085,7 +2085,7 @@
         <v>4</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>4</v>
@@ -2094,7 +2094,7 @@
         <v>34</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>1</v>
@@ -2108,66 +2108,66 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2191,111 +2191,111 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="M34" s="12" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H35" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N35" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2305,39 +2305,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
         <v>44</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="N36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>87</v>
@@ -2386,10 +2386,10 @@
         <v>11</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
@@ -2403,17 +2403,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2423,39 +2423,39 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2486,28 +2486,28 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>2</v>
@@ -2544,7 +2544,7 @@
         <v>32</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
@@ -2576,95 +2576,95 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>05625</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA RAVEGNANA,  329</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="M41" s="12" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>05625</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA RAVEGNANA,  329</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I42" s="12" t="n">
         <v>21</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>57</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>15</v>
@@ -2673,10 +2673,10 @@
         <v>1</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
@@ -2690,52 +2690,48 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>05993</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
@@ -2749,55 +2745,59 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05993</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>0</v>
@@ -2849,10 +2849,10 @@
         <v>1</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>40</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3954</v>
+        <v>4115</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2759</v>
+        <v>2881</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1137</v>
+        <v>1217</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>94</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>101</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>50</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>80</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>4</v>
@@ -1074,31 +1074,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I15" s="12" t="n">
+        <v>177</v>
+      </c>
+      <c r="J15" s="12" t="n">
         <v>168</v>
       </c>
-      <c r="J15" s="12" t="n">
-        <v>163</v>
-      </c>
       <c r="K15" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1192,35 +1192,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>15</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1251,28 +1251,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>3</v>
@@ -1310,35 +1310,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="I19" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>123</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L19" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J19" s="12" t="n">
-        <v>119</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>61</v>
-      </c>
       <c r="M19" s="12" t="n">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1369,35 +1369,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1428,28 +1428,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>8</v>
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>156</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I22" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="H22" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>125</v>
-      </c>
       <c r="J22" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>9</v>
@@ -1546,35 +1546,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>15</v>
@@ -1623,13 +1623,13 @@
         <v>42</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>141</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>96</v>
@@ -1685,7 +1685,7 @@
         <v>42</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1723,28 +1723,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1782,28 +1782,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>71</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>9</v>
@@ -1862,7 +1862,7 @@
         <v>29</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1900,28 +1900,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>59</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1935,72 +1935,76 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE 0290</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2010,115 +2014,111 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>TRIESTE 0290</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L32" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K32" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M32" s="12" t="n">
-        <v>116</v>
-      </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2128,46 +2128,46 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2191,35 +2191,35 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2250,28 +2250,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>6</v>
@@ -2285,17 +2285,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2305,35 +2305,35 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2344,17 +2344,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2364,56 +2364,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H37" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I37" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="J37" s="12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K37" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L37" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2423,56 +2423,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I38" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="N38" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="N38" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2482,35 +2482,35 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="H39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="N39" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2541,19 +2541,19 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>4</v>
@@ -2562,7 +2562,7 @@
         <v>2</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>1</v>
@@ -2600,28 +2600,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
@@ -2635,110 +2635,110 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05625</t>
+          <t>05993</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA RAVEGNANA,  329</t>
+          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>05993</t>
+          <t>05625</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
+          <t>VIA RAVEGNANA,  329</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2769,16 +2769,16 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>15</v>
@@ -2787,10 +2787,10 @@
         <v>1</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
@@ -2831,13 +2831,13 @@
         <v>18</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>20</v>
@@ -2849,10 +2849,10 @@
         <v>1</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O50" headerRowCount="1">
-  <autoFilter ref="A10:O50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O51" headerRowCount="1">
+  <autoFilter ref="A10:O51"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4115</v>
+        <v>4305</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2881</v>
+        <v>3039</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1217</v>
+        <v>1325</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>158</v>
@@ -877,51 +877,55 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>05635</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMEA NORD 102</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>S.S.423 LOC.TORRACCIA</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -932,59 +936,55 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>05635</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>S.S.423 LOC.TORRACCIA</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA ROMEA NORD 102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1015,28 +1015,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>80</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>4</v>
@@ -1050,17 +1050,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>JESI</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA ANCONA 68</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1070,39 +1070,39 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1133,31 +1133,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>102</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1168,17 +1168,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>JESI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>VIA ANCONA 68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1188,157 +1188,157 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>224</v>
+        <v>276</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA CARDUCCI</t>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="G18" s="12" t="n">
         <v>191</v>
       </c>
-      <c r="G18" s="12" t="n">
-        <v>244</v>
-      </c>
       <c r="H18" s="12" t="n">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE ADRIATICA 148</t>
+          <t>VIA CARDUCCI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1372,13 +1372,13 @@
         <v>187</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>72</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>150</v>
@@ -1390,7 +1390,7 @@
         <v>31</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>46</v>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>8</v>
@@ -1440,7 +1440,7 @@
         <v>40</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>28</v>
@@ -1449,10 +1449,10 @@
         <v>70</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1487,31 +1487,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>161</v>
       </c>
-      <c r="G22" s="12" t="n">
-        <v>156</v>
-      </c>
       <c r="H22" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>99</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1546,35 +1546,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1605,19 +1605,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>42</v>
@@ -1626,10 +1626,10 @@
         <v>48</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1664,28 +1664,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1726,13 +1726,13 @@
         <v>120</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>73</v>
@@ -1744,10 +1744,10 @@
         <v>51</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1782,28 +1782,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1841,28 +1841,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1900,28 +1900,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>59</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -2018,35 +2018,35 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2108,55 +2108,55 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="K33" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L33" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="M33" s="12" t="n">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2167,17 +2167,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2187,98 +2187,98 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2309,28 +2309,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>2</v>
@@ -2368,31 +2368,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2427,28 +2427,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>4</v>
@@ -2486,10 +2486,10 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>4</v>
@@ -2498,16 +2498,16 @@
         <v>9</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>1</v>
@@ -2521,165 +2521,169 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>COTIGNOLA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA MADONNA DI GENOVA, 23/A</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>COTIGNOLA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA MADONNA DI GENOVA, 23/A</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K41" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L41" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>05993</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2690,95 +2694,91 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>05625</t>
+          <t>05993</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA RAVEGNANA,  329</t>
+          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>05625</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA RAVEGNANA,  329</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>15</v>
@@ -2787,10 +2787,10 @@
         <v>1</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
@@ -2804,17 +2804,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2824,39 +2824,39 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3140,6 +3140,61 @@
       <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>07285</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>PEDASO</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>P.ZZA ROMA 2A</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>MORETTI MARCO MARIA</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="N51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O51" headerRowCount="1">
-  <autoFilter ref="A10:O51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O54" headerRowCount="1">
+  <autoFilter ref="A10:O54"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4305</v>
+        <v>4717</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3039</v>
+        <v>3338</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1325</v>
+        <v>1451</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -877,110 +877,114 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>05820</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>S.S.423 LOC.TORRACCIA</t>
+          <t>VIA BOLOGNA 632</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>203</v>
+        <v>528</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>64</v>
+        <v>392</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>281</v>
+        <v>550</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>05635</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMEA NORD 102</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
+          <t>S.S.423 LOC.TORRACCIA</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -991,173 +995,169 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>05918</t>
+          <t>05635</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA EMILIA, 1837</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>VIA ROMEA NORD 102</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>316</v>
+        <v>253</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="K14" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="L14" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="L14" s="12" t="n">
-        <v>80</v>
-      </c>
       <c r="M14" s="12" t="n">
-        <v>167</v>
+        <v>257</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>4</v>
+        <v>159</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>05918</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SANTARCANGELO DI ROMAGNA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>VIA EMILIA, 1837</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>227</v>
+        <v>316</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
         <v>228</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>349</v>
+        <v>153</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1168,194 +1168,194 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>JESI</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA ANCONA 68</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>276</v>
+        <v>220</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>201</v>
+        <v>349</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06019</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MISANO ADRIATICO</t>
+          <t>JESI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE ADRIATICA 148</t>
+          <t>VIA ANCONA 68</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>191</v>
+        <v>276</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>65</v>
+        <v>188</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>261</v>
+        <v>201</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>06019</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>MISANO ADRIATICO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA CARDUCCI</t>
+          <t>VIA NAZIONALE ADRIATICA 148</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MANZONI LOC. VILLA PAPA</t>
+          <t>VIA CARDUCCI</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,52 +1369,52 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="G20" s="12" t="n">
+        <v>256</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="I20" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>68</v>
-      </c>
       <c r="J20" s="12" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA E. MATTEI, 28</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1424,115 +1424,115 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>230</v>
+        <v>181</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMEA 1498</t>
+          <t>VIA E. MATTEI, 28</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>145</v>
+        <v>257</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA ROMEA 1498</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1542,56 +1542,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>208</v>
+        <v>145</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53970</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA CALCINARO 2460</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1601,94 +1601,94 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>VIA CALCINARO 2460</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>174</v>
+        <v>223</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1699,55 +1699,55 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>05941</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FORLÌ</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA EUGENIO BERTINI</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>136</v>
+        <v>37</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>565</v>
+        <v>57</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1758,55 +1758,55 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>05941</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>FORLÌ</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MONTAGNOLA N.24</t>
+          <t>VIA EUGENIO BERTINI</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>135</v>
+        <v>565</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1817,17 +1817,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>VIA DELLA MONTAGNOLA N.24</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1837,35 +1837,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1876,135 +1876,135 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>VIA RAVENNA 78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
+          <t>VIA MODENA, 236/P</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="K30" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L30" s="12" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,145 +2018,149 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>82</v>
+        <v>171</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE 0290</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>57</v>
-      </c>
       <c r="K32" s="12" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05982</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>MARECCHIESE LOC SPAD</t>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2167,17 +2171,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2187,94 +2191,90 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>TRIESTE 0290</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K35" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="K35" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L35" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2285,55 +2285,55 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>05982</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>MARECCHIESE LOC SPAD</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2344,17 +2344,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2368,52 +2368,52 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2427,52 +2427,52 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2482,35 +2482,35 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>40</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2521,17 +2521,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2541,90 +2541,94 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="N40" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M40" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="N40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>58176</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>COTIGNOLA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA MADONNA DI GENOVA, 23/A</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="N41" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="N41" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2635,17 +2639,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2655,111 +2659,115 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L42" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="N42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M42" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>05993</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SANTARCANGELO DI ROMAGNA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA MARECCHIESE,1600 LOC.S.ERMETE</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr"/>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K43" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="L43" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05625</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>COTIGNOLA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA RAVEGNANA,  329</t>
+          <t>VIA MADONNA DI GENOVA, 23/A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -2769,31 +2777,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2804,17 +2812,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2824,115 +2832,111 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="K45" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L45" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="M45" s="12" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>06148</t>
+          <t>05625</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>CAGLI</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA RAVEGNANA,  329</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SS 16 ADRIATICA KM 237+192 S.N.</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2942,142 +2946,150 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>06128</t>
+          <t>06148</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>CAGLI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>STRADA DELLE REGIONI KM 6 + 531</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>VIA FLAMINIA</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>06812</t>
+          <t>53821</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MONTECOSARO</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SS 485 KM8+126 STAZ.DI MONTECOSARO</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>SS 16 ADRIATICA KM 237+192 S.N.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="12" t="n">
+      <c r="L49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M49" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>0</v>
@@ -3091,36 +3103,36 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>51486</t>
+          <t>05861</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CORRIDONIA</t>
+          <t>COPPARO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>PAUSOLA ZONA INDUSTRIALE</t>
+          <t>VIA PRIMICELLO 26</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>0</v>
@@ -3139,60 +3151,225 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>07285</t>
+          <t>06128</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>PEDASO</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>P.ZZA ROMA 2A</t>
+          <t>STRADA DELLE REGIONI KM 6 + 531</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>DI VIRGILIO DAVID</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>06812</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>MONTECOSARO</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>SS 485 KM8+126 STAZ.DI MONTECOSARO</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>STROLOGO FRANCESCO</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>51486</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDONIA</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>PAUSOLA ZONA INDUSTRIALE</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>STROLOGO FRANCESCO</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>07285</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>PEDASO</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>P.ZZA ROMA 2A</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="12" t="n">
+      <c r="F54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
+      <c r="N54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CARSETTI MASSIMILIANO.xlsx
@@ -684,13 +684,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4717</v>
+        <v>4673</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3338</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1451</v>
+        <v>1415</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>193</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>105</v>
@@ -863,10 +863,10 @@
         <v>89</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>392</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>79</v>
@@ -922,7 +922,7 @@
         <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>24</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>104</v>
@@ -981,14 +981,14 @@
         <v>48</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>79</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>117</v>
@@ -1036,10 +1036,10 @@
         <v>63</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,19 +1074,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>63</v>
@@ -1095,7 +1095,7 @@
         <v>80</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>4</v>
@@ -1109,55 +1109,55 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>FAENZA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>GRANAROLO, 177</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>153</v>
+        <v>348</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1168,76 +1168,76 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FAENZA</t>
+          <t>JESI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>GRANAROLO, 177</t>
+          <t>VIA ANCONA 68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
         <v>228</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>349</v>
+        <v>197</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>JESI</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA ANCONA 68</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1247,39 +1247,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>188</v>
+        <v>105</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>65</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>51</v>
@@ -1331,7 +1331,7 @@
         <v>72</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>6</v>
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>47</v>
@@ -1390,7 +1390,7 @@
         <v>55</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>3</v>
@@ -1404,17 +1404,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MANZONI LOC. VILLA PAPA</t>
+          <t>VIA E. MATTEI, 28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1424,56 +1424,56 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>191</v>
+        <v>257</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA E. MATTEI, 28</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1483,56 +1483,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="I22" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>183</v>
+      </c>
+      <c r="N22" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="J22" s="12" t="n">
-        <v>112</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>257</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05911</t>
+          <t>05915</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CESENA</t>
+          <t>RIMINI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMEA 1498</t>
+          <t>VIA FLAMINIA 3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1542,35 +1542,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CELLINI LUCA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1581,17 +1581,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05915</t>
+          <t>05911</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>RIMINI</t>
+          <t>CESENA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA 3</t>
+          <t>VIA ROMEA 1498</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1601,39 +1601,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CELLINI LUCA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
         <v>147</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>18</v>
@@ -1676,7 +1676,7 @@
         <v>26</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>42</v>
@@ -1685,7 +1685,7 @@
         <v>48</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>38</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>183</v>
@@ -1735,7 +1735,7 @@
         <v>57</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>41</v>
@@ -1744,7 +1744,7 @@
         <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>2</v>
@@ -1782,19 +1782,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>18</v>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>21</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>18</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>20</v>
@@ -1921,7 +1921,7 @@
         <v>13</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1935,135 +1935,135 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA MODENA, 236/P</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>LIBANORI FEDERICO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
         <v>74</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>VIA MODENA, 236/P</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LIBANORI FEDERICO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="H31" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L31" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2073,35 +2073,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2132,35 +2132,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
         <v>67</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>1</v>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>32</v>
@@ -2216,69 +2216,73 @@
         <v>1</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>RAVENNA</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE 0290</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
+          <t>FRAZ. ASPIO SS 16</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>CALIO' ANTONELLA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2313,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>43</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>24</v>
@@ -2344,76 +2348,72 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>RAVENNA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>TRIESTE 0290</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CALIO' ANTONELLA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L37" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2423,56 +2423,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2486,31 +2486,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2521,17 +2521,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2541,56 +2541,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2600,35 +2600,35 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L41" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="M41" s="12" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2639,17 +2639,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2659,39 +2659,39 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
@@ -2734,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>16</v>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>4</v>
@@ -2789,7 +2789,7 @@
         <v>26</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>7</v>
@@ -2798,7 +2798,7 @@
         <v>2</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>2</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>2</v>
@@ -2848,7 +2848,7 @@
         <v>2</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>16</v>
@@ -2903,7 +2903,7 @@
         <v>21</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>1</v>
@@ -2956,13 +2956,13 @@
         <v>38</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>1</v>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>1</v>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3074,13 +3074,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>1</v>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3126,13 +3126,13 @@
         <v>0</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>0</v>
@@ -3236,13 +3236,13 @@
         <v>0</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
